--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="O208" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="R208" t="n">
-        <v>0.1616037200588708</v>
+        <v>0.1983318382540687</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -40310,12 +40310,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40340,22 +40340,22 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R235" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -40388,42 +40388,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40455,12 +40455,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40494,13 +40494,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -40533,42 +40533,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -40600,12 +40600,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -40639,95 +40639,81 @@
         </is>
       </c>
       <c r="N237" t="n">
+        <v>2</v>
+      </c>
+      <c r="O237" t="n">
+        <v>2</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="n">
         <v>0</v>
       </c>
-      <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO237" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP237" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT237" t="n">
-        <v>1</v>
-      </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40754,7 +40740,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -40803,98 +40789,23 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U238" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -40960,6 +40871,240 @@
         </is>
       </c>
       <c r="BC238" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -41081,7 +41226,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -41091,7 +41236,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -41143,7 +41288,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1134</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O208" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R208" t="n">
-        <v>0.1983318382540687</v>
+        <v>0.2056774618931082</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -40639,13 +40639,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R237" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -36891,12 +36891,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -36930,13 +36930,16 @@
         </is>
       </c>
       <c r="N215" t="n">
+        <v>153</v>
+      </c>
+      <c r="O215" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q215" t="n">
         <v>0</v>
       </c>
-      <c r="O215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>0.01082868387011628</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -36969,42 +36972,42 @@
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -37036,12 +37039,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -37075,95 +37078,81 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37190,7 +37179,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -37239,98 +37228,23 @@
       <c r="O217" t="n">
         <v>1</v>
       </c>
+      <c r="R217" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U217" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -37424,17 +37338,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -37468,81 +37382,170 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O218" t="n">
-        <v>10</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0.002865038132769385</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37574,12 +37577,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -37604,7 +37607,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -37613,13 +37616,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O219" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R219" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -37652,42 +37655,42 @@
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37719,12 +37722,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -37758,93 +37761,81 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O220" t="n">
-        <v>1</v>
-      </c>
-      <c r="P220" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R220" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37871,7 +37862,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -37923,98 +37914,18 @@
       <c r="P221" t="n">
         <v>1</v>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R221" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -38108,17 +38019,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -38143,7 +38054,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -38152,81 +38063,173 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>13</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0.003724549572600201</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P222" t="n">
+        <v>1</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38258,12 +38261,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -38288,7 +38291,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -38297,13 +38300,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O223" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R223" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -38336,42 +38339,42 @@
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38403,12 +38406,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -38442,93 +38445,81 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O224" t="n">
-        <v>3</v>
-      </c>
-      <c r="P224" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R224" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38555,7 +38546,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -38607,98 +38598,18 @@
       <c r="P225" t="n">
         <v>3</v>
       </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R225" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
@@ -38792,17 +38703,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -38827,7 +38738,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -38836,81 +38747,173 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O226" t="n">
-        <v>7</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.00200552669293857</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P226" t="n">
+        <v>3</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38942,12 +38945,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -38972,7 +38975,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -38981,13 +38984,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O227" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R227" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -39020,42 +39023,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39087,12 +39090,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -39126,93 +39129,81 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O228" t="n">
-        <v>1</v>
-      </c>
-      <c r="P228" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R228" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39239,7 +39230,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -39291,98 +39282,18 @@
       <c r="P229" t="n">
         <v>1</v>
       </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R229" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN229" t="b">
-        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -39476,17 +39387,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -39511,7 +39422,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -39520,81 +39431,173 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O230" t="n">
-        <v>10</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0.002865038132769385</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P230" t="n">
+        <v>1</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39626,12 +39629,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -39656,7 +39659,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -39665,13 +39668,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O231" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R231" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -39704,42 +39707,42 @@
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39771,12 +39774,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -39810,93 +39813,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
-      </c>
-      <c r="P232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R232" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39923,7 +39914,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -39975,98 +39966,18 @@
       <c r="P233" t="n">
         <v>1</v>
       </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R233" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
@@ -40160,17 +40071,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -40195,7 +40106,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -40204,81 +40115,173 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O234" t="n">
-        <v>17</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0.004870564825707955</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P234" t="n">
+        <v>1</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40310,12 +40313,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40340,7 +40343,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -40349,13 +40352,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O235" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="R235" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.004870564825707955</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -40388,42 +40391,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40455,12 +40458,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40485,22 +40488,22 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R236" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -40533,42 +40536,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40600,12 +40603,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -40630,90 +40633,102 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N237" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="P237" t="n">
+        <v>1</v>
       </c>
       <c r="R237" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40740,17 +40755,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -40775,37 +40790,115 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P238" t="n">
+        <v>1</v>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -40814,7 +40907,7 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
@@ -40824,55 +40917,55 @@
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
         </is>
       </c>
       <c r="AT238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40899,214 +40992,808 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" t="n">
+        <v>1</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
+      <c r="AT239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>3</v>
+      </c>
+      <c r="O240" t="n">
+        <v>3</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA240" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>D065</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>Monkeypox</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
         <is>
           <t>猴痘</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="K242" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N239" t="n">
+      <c r="N242" t="n">
         <v>0</v>
       </c>
-      <c r="O239" t="n">
+      <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="U242" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V239" t="inlineStr">
+      <c r="V242" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="W239" t="inlineStr">
+      <c r="W242" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X239" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>M-kopper</t>
         </is>
       </c>
-      <c r="Y239" t="inlineStr">
+      <c r="Y242" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z239" t="inlineStr">
+      <c r="Z242" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA239" t="inlineStr">
+      <c r="AA242" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB239" t="inlineStr">
+      <c r="AB242" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC239" t="inlineStr">
+      <c r="AC242" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD239" t="inlineStr">
+      <c r="AD242" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE239" t="inlineStr">
+      <c r="AE242" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF239" t="inlineStr">
+      <c r="AF242" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG239" t="inlineStr">
+      <c r="AG242" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH239" t="inlineStr">
+      <c r="AH242" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI239" t="inlineStr">
+      <c r="AI242" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ239" t="inlineStr">
+      <c r="AJ242" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK239" t="inlineStr">
+      <c r="AK242" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM239" t="inlineStr">
+      <c r="AM242" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN239" t="b">
+      <c r="AN242" t="b">
         <v>1</v>
       </c>
-      <c r="AO239" t="inlineStr">
+      <c r="AO242" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP239" t="inlineStr">
+      <c r="AP242" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ239" t="inlineStr">
+      <c r="AQ242" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS239" t="inlineStr">
+      <c r="AS242" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="AT239" t="n">
+      <c r="AT242" t="n">
         <v>1</v>
       </c>
-      <c r="AU239" t="inlineStr">
+      <c r="AU242" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV239" t="inlineStr">
+      <c r="AV242" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW239" t="inlineStr">
+      <c r="AW242" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX239" t="inlineStr">
+      <c r="AX242" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY239" t="inlineStr">
+      <c r="AY242" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ239" t="inlineStr">
+      <c r="AZ242" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA239" t="inlineStr">
+      <c r="BA242" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB239" t="inlineStr">
+      <c r="BB242" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC239" t="inlineStr">
+      <c r="BC242" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>13</v>
+      </c>
+      <c r="O243" t="n">
+        <v>13</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41143,7 +41830,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -41226,7 +41913,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -41236,7 +41923,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -41256,7 +41943,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -41288,7 +41975,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1152</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -36323,13 +36323,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O210" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R210" t="n">
-        <v>0.2056774618931082</v>
+        <v>0.2130230855321478</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1319</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -41571,13 +41571,13 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O242" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R242" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -42184,6 +42184,151 @@
       <c r="BC245" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>6</v>
+      </c>
+      <c r="O246" t="n">
+        <v>6</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42220,7 +42365,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -42303,7 +42448,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -42313,7 +42458,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -42365,7 +42510,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1321</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -32904,13 +32904,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0.01891260466471829</v>
+        <v>0</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -33063,10 +33063,10 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
@@ -37967,12 +37967,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -38006,81 +38006,95 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38107,17 +38121,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -38142,7 +38156,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -38151,56 +38165,145 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
-        <v>7</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly mpox notifications.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -38210,17 +38313,17 @@
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
@@ -38257,12 +38360,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -38287,7 +38390,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -38296,93 +38399,81 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O223" t="n">
-        <v>1</v>
-      </c>
-      <c r="P223" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R223" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38409,17 +38500,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -38453,173 +38544,81 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O224" t="n">
-        <v>1</v>
-      </c>
-      <c r="P224" t="n">
-        <v>1</v>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38651,12 +38650,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -38681,7 +38680,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -38690,81 +38689,93 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O225" t="n">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="P225" t="n">
+        <v>1</v>
       </c>
       <c r="R225" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38791,17 +38802,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -38826,7 +38837,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -38835,81 +38846,173 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>6</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P226" t="n">
+        <v>1</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38941,12 +39044,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -38971,7 +39074,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -38980,93 +39083,81 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O227" t="n">
-        <v>3</v>
-      </c>
-      <c r="P227" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R227" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39093,17 +39184,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -39137,173 +39228,81 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O228" t="n">
-        <v>3</v>
-      </c>
-      <c r="P228" t="n">
-        <v>3</v>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE228" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG228" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ228" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK228" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM228" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN228" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39335,12 +39334,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -39365,7 +39364,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -39374,81 +39373,93 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O229" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="P229" t="n">
+        <v>3</v>
       </c>
       <c r="R229" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.05079797265291142</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39475,17 +39486,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -39510,7 +39521,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -39519,81 +39530,173 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O230" t="n">
-        <v>4</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P230" t="n">
+        <v>3</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39625,12 +39728,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -39655,7 +39758,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -39664,93 +39767,81 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O231" t="n">
-        <v>1</v>
-      </c>
-      <c r="P231" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R231" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39777,17 +39868,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -39821,173 +39912,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
-      </c>
-      <c r="P232" t="n">
-        <v>1</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40019,12 +40018,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -40049,7 +40048,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -40058,81 +40057,93 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="P233" t="n">
+        <v>1</v>
       </c>
       <c r="R233" t="n">
-        <v>0.002865038132769385</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40159,17 +40170,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -40194,7 +40205,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -40203,81 +40214,173 @@
         </is>
       </c>
       <c r="N234" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" t="n">
+        <v>1</v>
+      </c>
+      <c r="P234" t="n">
+        <v>1</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT234" t="n">
         <v>2</v>
       </c>
-      <c r="O234" t="n">
-        <v>2</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO234" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP234" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
-      <c r="AT234" t="n">
-        <v>0</v>
-      </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40309,12 +40412,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40339,7 +40442,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -40348,93 +40451,81 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
-      </c>
-      <c r="P235" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R235" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA235" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40461,17 +40552,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40505,173 +40596,81 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
-      </c>
-      <c r="P236" t="n">
-        <v>1</v>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40703,12 +40702,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -40733,7 +40732,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -40742,81 +40741,93 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O237" t="n">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="P237" t="n">
+        <v>1</v>
       </c>
       <c r="R237" t="n">
-        <v>0.004870564825707955</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40843,17 +40854,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -40878,7 +40889,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -40887,81 +40898,173 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O238" t="n">
-        <v>3</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P238" t="n">
+        <v>1</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40993,12 +41096,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -41023,7 +41126,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -41032,93 +41135,81 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O239" t="n">
-        <v>1</v>
-      </c>
-      <c r="P239" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R239" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.004870564825707955</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41145,17 +41236,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -41189,173 +41280,81 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O240" t="n">
-        <v>1</v>
-      </c>
-      <c r="P240" t="n">
-        <v>1</v>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN240" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41387,12 +41386,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -41417,12 +41416,12 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N241" t="n">
@@ -41431,76 +41430,88 @@
       <c r="O241" t="n">
         <v>1</v>
       </c>
+      <c r="P241" t="n">
+        <v>1</v>
+      </c>
       <c r="R241" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41527,17 +41538,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -41562,90 +41573,182 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O242" t="n">
-        <v>4</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.007751879695168184</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P242" t="n">
+        <v>1</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41677,12 +41780,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -41716,95 +41819,81 @@
         </is>
       </c>
       <c r="N243" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" t="n">
+        <v>1</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
         <v>0</v>
       </c>
-      <c r="O243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO243" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP243" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT243" t="n">
-        <v>1</v>
-      </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -41831,17 +41920,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -41875,170 +41964,81 @@
         </is>
       </c>
       <c r="N244" t="n">
+        <v>4</v>
+      </c>
+      <c r="O244" t="n">
+        <v>4</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.007751879695168184</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="n">
         <v>0</v>
       </c>
-      <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT244" t="n">
-        <v>1</v>
-      </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -42070,12 +42070,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -42100,7 +42100,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -42109,81 +42109,95 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>0.003724549572600201</v>
+        <v>0</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42210,123 +42224,502 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>13</v>
+      </c>
+      <c r="O247" t="n">
+        <v>13</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
+      <c r="AT247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G248" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>D065</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>Monkeypox</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
         <is>
           <t>猴痘</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="K248" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="L248" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N246" t="n">
+      <c r="N248" t="n">
         <v>6</v>
       </c>
-      <c r="O246" t="n">
+      <c r="O248" t="n">
         <v>6</v>
       </c>
-      <c r="R246" t="n">
+      <c r="R248" t="n">
         <v>0.004900850445394598</v>
       </c>
-      <c r="S246" t="inlineStr">
+      <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO246" t="inlineStr">
+      <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP246" t="inlineStr">
+      <c r="AP248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR246" t="inlineStr">
+      <c r="AR248" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS246" t="inlineStr"/>
-      <c r="AT246" t="n">
+      <c r="AS248" t="inlineStr"/>
+      <c r="AT248" t="n">
         <v>0</v>
       </c>
-      <c r="AU246" t="inlineStr">
+      <c r="AU248" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV246" t="inlineStr">
+      <c r="AV248" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW246" t="inlineStr">
+      <c r="AW248" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX246" t="inlineStr">
+      <c r="AX248" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY246" t="inlineStr">
+      <c r="AY248" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ246" t="inlineStr">
+      <c r="AZ248" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA246" t="inlineStr">
+      <c r="BA248" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB246" t="inlineStr">
+      <c r="BB248" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC246" t="inlineStr">
+      <c r="BC248" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -42448,7 +42841,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -42458,7 +42851,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -42478,7 +42871,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -42510,7 +42903,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -42109,13 +42109,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -42268,10 +42268,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -36323,13 +36323,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O210" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R210" t="n">
-        <v>0.2130230855321478</v>
+        <v>0.2203687091711874</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -42722,6 +42722,545 @@
       <c r="BC248" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>1</v>
+      </c>
+      <c r="O249" t="n">
+        <v>1</v>
+      </c>
+      <c r="P249" t="n">
+        <v>1</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA249" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB249" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC249" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" t="n">
+        <v>1</v>
+      </c>
+      <c r="P250" t="n">
+        <v>1</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>13</v>
+      </c>
+      <c r="O251" t="n">
+        <v>13</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.003724549572600201</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42758,7 +43297,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -42841,7 +43380,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -42851,7 +43390,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -42871,7 +43410,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -42903,7 +43442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1328</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -36323,13 +36323,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O210" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R210" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.2240415209907072</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -37429,12 +37429,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -37468,13 +37468,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>0.05421081120786837</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -37507,42 +37507,42 @@
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -37574,12 +37574,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -37613,95 +37613,81 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37728,7 +37714,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -37777,98 +37763,23 @@
       <c r="O220" t="n">
         <v>1</v>
       </c>
+      <c r="R220" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U220" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN220" t="b">
-        <v>1</v>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
@@ -37962,17 +37873,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -38006,22 +37917,39 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -38029,6 +37957,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -38046,7 +38032,7 @@
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
+          <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -38059,42 +38045,42 @@
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38121,7 +38107,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -38170,98 +38156,23 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U222" t="inlineStr">
         <is>
           <t>SER_NZ_MPOX_MONTHLY</t>
         </is>
       </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_NZ_MPOX_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly mpox notifications.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
@@ -38355,17 +38266,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -38399,81 +38310,170 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>10</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0.002865038132769385</v>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly mpox notifications.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_NZ_MPOX_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38505,12 +38505,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -38535,7 +38535,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -38544,13 +38544,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O224" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R224" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -38583,42 +38583,42 @@
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38650,12 +38650,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -38689,93 +38689,81 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O225" t="n">
-        <v>1</v>
-      </c>
-      <c r="P225" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R225" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.005717658852960364</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA225" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38802,7 +38790,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -38854,98 +38842,18 @@
       <c r="P226" t="n">
         <v>1</v>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R226" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE226" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF226" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG226" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH226" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ226" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK226" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM226" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN226" t="b">
-        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
@@ -39039,17 +38947,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -39074,7 +38982,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -39083,81 +38991,173 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O227" t="n">
-        <v>13</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0.003724549572600201</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P227" t="n">
+        <v>1</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39189,12 +39189,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -39219,7 +39219,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -39228,13 +39228,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O228" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R228" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -39267,42 +39267,42 @@
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39334,12 +39334,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -39373,93 +39373,81 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O229" t="n">
-        <v>3</v>
-      </c>
-      <c r="P229" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R229" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39486,7 +39474,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -39538,98 +39526,18 @@
       <c r="P230" t="n">
         <v>3</v>
       </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R230" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN230" t="b">
-        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
@@ -39723,17 +39631,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -39758,7 +39666,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -39767,81 +39675,173 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O231" t="n">
-        <v>7</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0.00200552669293857</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P231" t="n">
+        <v>3</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39873,12 +39873,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -39903,7 +39903,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -39912,13 +39912,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O232" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R232" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -39951,42 +39951,42 @@
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40018,12 +40018,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -40057,93 +40057,81 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
-      </c>
-      <c r="P233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R233" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA233" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40170,7 +40158,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -40222,98 +40210,18 @@
       <c r="P234" t="n">
         <v>1</v>
       </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R234" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN234" t="b">
-        <v>1</v>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
@@ -40407,17 +40315,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -40442,7 +40350,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -40451,81 +40359,173 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>10</v>
-      </c>
-      <c r="R235" t="n">
-        <v>0.002865038132769385</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P235" t="n">
+        <v>1</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40557,12 +40557,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -40587,7 +40587,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -40596,13 +40596,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O236" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R236" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -40635,42 +40635,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40702,12 +40702,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -40741,93 +40741,81 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O237" t="n">
-        <v>1</v>
-      </c>
-      <c r="P237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R237" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40854,7 +40842,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -40906,98 +40894,18 @@
       <c r="P238" t="n">
         <v>1</v>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R238" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
@@ -41091,17 +40999,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -41126,7 +41034,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -41135,81 +41043,173 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>17</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0.004870564825707955</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P239" t="n">
+        <v>1</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
+        <v>1</v>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41241,12 +41241,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -41271,7 +41271,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -41280,13 +41280,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O240" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="R240" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.004870564825707955</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -41319,42 +41319,42 @@
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41386,12 +41386,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -41425,93 +41425,81 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O241" t="n">
-        <v>1</v>
-      </c>
-      <c r="P241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R241" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41538,7 +41526,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -41590,98 +41578,18 @@
       <c r="P242" t="n">
         <v>1</v>
       </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R242" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN242" t="b">
-        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
@@ -41775,17 +41683,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -41810,12 +41718,12 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N243" t="n">
@@ -41824,76 +41732,168 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
-      <c r="R243" t="n">
-        <v>0.00367281181951979</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P243" t="n">
+        <v>1</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN243" t="b">
+        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
       <c r="AT243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41925,12 +41925,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -41964,13 +41964,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O244" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R244" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -42003,42 +42003,42 @@
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -42070,12 +42070,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -42109,95 +42109,81 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R245" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -42224,7 +42210,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -42268,103 +42254,28 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O246" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
           <t>SER_NO_FHI_714_MONTHLY</t>
         </is>
       </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_714_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>M-kopper</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN246" t="b">
-        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
@@ -42458,17 +42369,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -42493,7 +42404,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -42502,81 +42413,170 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O247" t="n">
-        <v>13</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0.003724549572600201</v>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>M-kopper</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN247" t="b">
+        <v>1</v>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_714_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42608,12 +42608,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -42647,13 +42647,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O248" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R248" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -42686,42 +42686,42 @@
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42753,12 +42753,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -42792,93 +42792,81 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O249" t="n">
-        <v>1</v>
-      </c>
-      <c r="P249" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R249" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ249" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42905,7 +42893,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -42957,98 +42945,18 @@
       <c r="P250" t="n">
         <v>1</v>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MPOX</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>Mpox</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R250" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN250" t="b">
-        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
@@ -43142,123 +43050,1044 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" t="n">
+        <v>1</v>
+      </c>
+      <c r="P251" t="n">
+        <v>1</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F252" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G252" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>D065</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Monkeypox</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
         <is>
           <t>猴痘</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K252" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="L252" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N251" t="n">
+      <c r="N252" t="n">
         <v>13</v>
       </c>
-      <c r="O251" t="n">
+      <c r="O252" t="n">
         <v>13</v>
       </c>
-      <c r="R251" t="n">
+      <c r="R252" t="n">
         <v>0.003724549572600201</v>
       </c>
-      <c r="S251" t="inlineStr">
+      <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO251" t="inlineStr">
+      <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP251" t="inlineStr">
+      <c r="AP252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR251" t="inlineStr">
+      <c r="AR252" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS251" t="inlineStr"/>
-      <c r="AT251" t="n">
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="n">
         <v>0</v>
       </c>
-      <c r="AU251" t="inlineStr">
+      <c r="AU252" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV251" t="inlineStr">
+      <c r="AV252" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW251" t="inlineStr">
+      <c r="AW252" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX251" t="inlineStr">
+      <c r="AX252" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY251" t="inlineStr">
+      <c r="AY252" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ251" t="inlineStr">
+      <c r="AZ252" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA251" t="inlineStr">
+      <c r="BA252" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB251" t="inlineStr">
+      <c r="BB252" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC251" t="inlineStr">
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>5</v>
+      </c>
+      <c r="O253" t="n">
+        <v>5</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" t="n">
+        <v>1</v>
+      </c>
+      <c r="P254" t="n">
+        <v>1</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="n">
+        <v>1</v>
+      </c>
+      <c r="P255" t="n">
+        <v>1</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>16</v>
+      </c>
+      <c r="O256" t="n">
+        <v>16</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0.004584061012431017</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -43297,7 +44126,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -43380,7 +44209,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -43390,7 +44219,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -43410,7 +44239,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -43442,7 +44271,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1345</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -52884,13 +52884,13 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="O300" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="R300" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.1175299782246333</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
@@ -53029,13 +53029,13 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O301" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R301" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S301" t="inlineStr">
         <is>
@@ -55010,6 +55010,835 @@
       <c r="BC312" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>2</v>
+      </c>
+      <c r="O313" t="n">
+        <v>2</v>
+      </c>
+      <c r="R313" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR313" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr"/>
+      <c r="AT313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU313" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV313" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>4</v>
+      </c>
+      <c r="O314" t="n">
+        <v>4</v>
+      </c>
+      <c r="P314" t="n">
+        <v>4</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU314" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV314" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW314" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX314" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY314" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA314" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB314" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC314" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>4</v>
+      </c>
+      <c r="O315" t="n">
+        <v>4</v>
+      </c>
+      <c r="P315" t="n">
+        <v>4</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>Mpox</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN315" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MPOX; SER_SG_HIST_MPOX</t>
+        </is>
+      </c>
+      <c r="AT315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY315" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>21</v>
+      </c>
+      <c r="O316" t="n">
+        <v>21</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0.006016580078815709</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr"/>
+      <c r="AT316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr"/>
+      <c r="AT317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -55046,7 +55875,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -55129,7 +55958,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
@@ -55139,7 +55968,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="11">
@@ -55159,7 +55988,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -55191,7 +56020,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1590</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -17325,7 +17325,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -22769,7 +22769,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -31950,7 +31950,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -40952,7 +40952,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -48929,7 +48929,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -53174,13 +53174,13 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R302" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
@@ -53333,10 +53333,10 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U303" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -56020,7 +56020,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -60686,13 +60686,13 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O349" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R349" t="n">
-        <v>0.1285484136831927</v>
+        <v>0.1358940373222322</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -65949,6 +65949,151 @@
       <c r="BC380" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>5</v>
+      </c>
+      <c r="O381" t="n">
+        <v>5</v>
+      </c>
+      <c r="R381" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR381" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr"/>
+      <c r="AT381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU381" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV381" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW381" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX381" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY381" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA381" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB381" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC381" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -65985,7 +66130,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -66068,7 +66213,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -66078,7 +66223,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11">
@@ -66130,7 +66275,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1882</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d065/2026-2029.xlsx
+++ b/diseases/d065/2026-2029.xlsx
@@ -4275,9 +4275,6 @@
       <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -4970,9 +4967,6 @@
       <c r="O27" t="n">
         <v>12</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.003438045759323263</v>
       </c>
@@ -5665,9 +5659,6 @@
       <c r="O31" t="n">
         <v>11</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.003151541946046324</v>
       </c>
@@ -6360,9 +6351,6 @@
       <c r="O35" t="n">
         <v>15</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.004297557199154077</v>
       </c>
@@ -7055,9 +7043,6 @@
       <c r="O39" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -11260,9 +11245,6 @@
       <c r="O64" t="n">
         <v>13</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.003724549572600201</v>
       </c>
@@ -11955,9 +11937,6 @@
       <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -12650,9 +12629,6 @@
       <c r="O72" t="n">
         <v>7</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -13345,9 +13321,6 @@
       <c r="O76" t="n">
         <v>12</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.003438045759323263</v>
       </c>
@@ -17160,9 +17133,6 @@
       <c r="O99" t="n">
         <v>9</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -17855,9 +17825,6 @@
       <c r="O103" t="n">
         <v>9</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -18550,9 +18517,6 @@
       <c r="O107" t="n">
         <v>7</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -19245,9 +19209,6 @@
       <c r="O111" t="n">
         <v>14</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -23060,9 +23021,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -23755,9 +23713,6 @@
       <c r="O138" t="n">
         <v>5</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -24450,9 +24405,6 @@
       <c r="O142" t="n">
         <v>6</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -25145,9 +25097,6 @@
       <c r="O146" t="n">
         <v>9</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -29740,9 +29689,6 @@
       <c r="O173" t="n">
         <v>4</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -30435,9 +30381,6 @@
       <c r="O177" t="n">
         <v>6</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -31130,9 +31073,6 @@
       <c r="O181" t="n">
         <v>10</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -31825,9 +31765,6 @@
       <c r="O185" t="n">
         <v>5</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -66094,6 +66031,156 @@
       <c r="BC381" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>monkeypox</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N382" t="n">
+        <v>8</v>
+      </c>
+      <c r="O382" t="n">
+        <v>8</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0.002292030506215508</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO382" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP382" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR382" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr"/>
+      <c r="AT382" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU382" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV382" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW382" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX382" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY382" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA382" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB382" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC382" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66130,7 +66217,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -66213,7 +66300,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -66223,7 +66310,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11">
@@ -66275,7 +66362,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1889</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="16">
